--- a/docs/LIVE_SPOtCH_開発費用見積もり（参考）.xlsx
+++ b/docs/LIVE_SPOtCH_開発費用見積もり（参考）.xlsx
@@ -663,14 +663,14 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>残り開発分（8%）</t>
+          <t>残り開発分（8%）+ 保守・API費</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>775000</v>
+        <v>1365000</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>852500</v>
+        <v>1501500</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>8725000</v>
+        <v>9315000</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9597500</v>
+        <v>10246500</v>
       </c>
     </row>
     <row r="9">
@@ -2037,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2143,49 +2143,89 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>外部API利用料・インフラ増強</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>ローンチ後保守運用・追加開発</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="31" t="n">
-        <v>775000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="31" t="n">
+        <v>1365000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>消費税（10%）</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="27" t="n">
-        <v>77500</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>136500</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>合計（税込）</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="9" t="n">
-        <v>852500</v>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="9" t="n">
+        <v>1501500</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/LIVE_SPOtCH_開発費用見積もり（参考）.xlsx
+++ b/docs/LIVE_SPOtCH_開発費用見積もり（参考）.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="総合計" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積もり明細（完成分92%）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残り開発（8%）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完成分の見積もり明細" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残り開発（5月中完璧化）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人月単価の前提" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -607,10 +607,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -618,14 +618,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH 開発費用見積もり — 総合計</t>
+          <t>LIVE SPOtCH 開発費用見積もり (v2) — 総合計</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>一般的な開発会社に外注した場合の想定費用</t>
+          <t>一般的な開発会社に外注した場合の想定費用 ／ 5/10 時点 / 126 PR マージ反映</t>
         </is>
       </c>
     </row>
@@ -650,27 +650,27 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>現在完成分（92%）</t>
+          <t>完成分（5/10 時点 / 100% 本番稼働）</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7950000</v>
+        <v>13762500</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>8745000</v>
+        <v>15138750</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>残り開発分（8%）+ 保守・API費</t>
+          <t>残り開発（5月中完璧化 + 6/1 ローンチ後 1ヶ月保守）</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1365000</v>
+        <v>1445000</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1501500</v>
+        <v>1589500</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>9315000</v>
+        <v>15207500</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10246500</v>
+        <v>16728250</v>
       </c>
     </row>
     <row r="9">
@@ -696,51 +696,59 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>・上記は国内の中規模Web開発会社（従業員20〜50名程度）の標準的な見積もり水準です。</t>
+          <t>・上記は国内の中規模 Web 開発会社（従業員 20〜50 名程度）の標準的な見積もり水準です。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>・大手SIer（NTTデータ、富士通等）の場合、1,500万〜2,000万円以上になることもあります。</t>
+          <t>・大手 SIer（NTT データ、富士通等）の場合、1.5〜2 倍（2,000 万〜3,000 万円）になることもあります。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>・フリーランスへの発注の場合は、5割〜7割程度（約600万〜800万円）に抑えられる可能性があります。</t>
+          <t>・ライブ映像配信（LiveKit / WebRTC / RTMP push）+ YouTube Live 連携 + iOS Safari 対応は特殊技術のため、対応できる会社が限られ割増傾向です。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>・ライブ映像配信（LiveKit連携）は特殊技術のため、対応できる会社が限られ割増傾向です。</t>
+          <t>・5/10 までの 126 PR を踏まえ、配信品質改善・運用堅牢化・YouTube Live 連携 等の実装増分（+約 500 万円分）を反映した v2 改訂版です。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>・保守・運用費（月額）は含まれていません。通常、開発費の15〜20%/年が保守費用の相場です。</t>
+          <t>・保守・運用費（月額）はローンチ後 1ヶ月分のみ含みます。通常、開発費の 15〜20%/年 が保守費用の相場です。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>・本見積もりは、AI開発ツールを活用せず従来の手法で開発した場合の想定です。</t>
+          <t>・本見積もりは、AI 開発支援ツールを活用せず従来の手法で開発した場合の想定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>・当社は Claude 等の AI 駆動開発で、上記費用と同等の機能を実コストほぼゼロで実装しております（実績）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A12:C12"/>
@@ -758,12 +766,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
@@ -771,7 +779,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LIVE SPOtCH 開発費用見積もり（参考） — 現在完成分（92%）</t>
+          <t>LIVE SPOtCH 開発費用見積もり (v2) — 完成分 (5/10 時点 / 126 PR マージ)</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2. UI/UXデザイン</t>
+          <t>2. UI/UX デザイン</t>
         </is>
       </c>
       <c r="B9" s="13" t="n"/>
@@ -903,19 +911,19 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>ワイヤーフレーム設計（10画面）</t>
+          <t>ワイヤーフレーム設計（13画面）</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>デザイナー 0.3人月</t>
+          <t>デザイナー 0.4人月</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
         <v>700000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>210000</v>
+        <v>280000</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -926,19 +934,19 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>UIデザイン（10画面 + LP）</t>
+          <t>UIデザイン（13画面 + LP）</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>デザイナー 0.5人月</t>
+          <t>デザイナー 0.6人月</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>700000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>350000</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -949,19 +957,19 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>レスポンシブ対応設計</t>
+          <t>レスポンシブ対応設計（PC/タブレット/スマホ）</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>デザイナー 0.2人月</t>
+          <t>デザイナー 0.3人月</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
         <v>700000</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>140000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -973,12 +981,12 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>1.0人月</t>
+          <t>1.3人月</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr"/>
       <c r="E13" s="21" t="n">
-        <v>700000</v>
+        <v>910000</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1000,7 +1008,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Next.js環境構築・基盤設計</t>
+          <t>Next.js 環境構築・基盤設計</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -1023,7 +1031,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>認証画面（Google OAuth）</t>
+          <t>認証画面（Google OAuth + メール認証）</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1092,19 +1100,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>視聴画面（リアルタイムスコア更新）</t>
+          <t>視聴画面（リアルタイムスコア更新 + iframe 切替）</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>FE 0.3人月</t>
+          <t>FE 0.4人月</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>800000</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>240000</v>
+        <v>320000</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1115,7 +1123,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>スコアボードUI（スポーツ別ルール分岐）</t>
+          <t>スコアボード UI（スポーツ別ルール分岐）</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1138,19 +1146,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>マイページ（プロフィール編集・配信履歴）</t>
+          <t>マイページ（プロフィール編集・配信履歴・ストレイ警告）</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>FE 0.2人月</t>
+          <t>FE 0.3人月</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>800000</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>160000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -1166,14 +1174,14 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>FE 0.15人月</t>
+          <t>FE 0.2人月</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
         <v>800000</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>120000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -1207,19 +1215,19 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>PWA対応（manifest・ServiceWorker）</t>
+          <t>PWA 対応（manifest・ServiceWorker・iOS 対応）</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>FE 0.15人月</t>
+          <t>FE 0.2人月</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
         <v>800000</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>120000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1230,19 +1238,19 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>ボトムナビ・共通レイアウト</t>
+          <t>ボトムナビ・共通レイアウト・safe-area 対応</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>FE 0.15人月</t>
+          <t>FE 0.2人月</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>800000</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>120000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1254,12 +1262,12 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>2.5人月</t>
+          <t>2.8人月</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr"/>
       <c r="E26" s="21" t="n">
-        <v>1960000</v>
+        <v>2240000</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
@@ -1281,7 +1289,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Supabase設計・DBスキーマ設計</t>
+          <t>Supabase 設計・DB スキーマ設計</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -1327,7 +1335,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>配信CRUD（broadcasts テーブル操作）</t>
+          <t>配信 CRUD（broadcasts テーブル操作）</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -1373,7 +1381,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>LiveKit連携（トークンAPI・映像配信制御）</t>
+          <t>LiveKit 連携（トークン API・WebRTC publish 制御）</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -1419,7 +1427,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Stripe決済（Checkout・Webhook・顧客ポータル）</t>
+          <t>Stripe 決済（Checkout・Webhook・顧客ポータル）</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -1447,14 +1455,14 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>BE 0.3人月</t>
+          <t>BE 0.4人月</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
         <v>900000</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>270000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -1465,19 +1473,19 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>YouTube OAuth連携（認証・トークン管理）</t>
+          <t>スケジュール管理（配信予定・チームフィルタ）</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>BE 0.3人月</t>
+          <t>BE 0.2人月</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
         <v>900000</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>270000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
@@ -1488,7 +1496,7 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>パスワードリセット・お問い合わせAPI</t>
+          <t>パスワードリセット・お問い合わせ API</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
@@ -1511,7 +1519,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>プロフィール管理・退会API（Stripe解約連動）</t>
+          <t>プロフィール管理・退会 API（Stripe 解約連動）</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -1534,7 +1542,7 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>LINE共有・共有コード生成</t>
+          <t>LINE 共有・共有コード生成・QR コード</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -1550,88 +1558,88 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>4-13</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>セキュリティ対策（RLS・トライアル検証・Cron）</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>BE 0.2人月</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n">
+      <c r="A40" s="18" t="inlineStr"/>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>2.9人月</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr"/>
+      <c r="E40" s="21" t="n">
+        <v>2610000</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>5. インフラ構築・デプロイ</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Vercel デプロイ設定 + 独自ドメイン (live-spotch.com)</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>インフラ 0.1人月</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
         <v>900000</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="18" t="inlineStr"/>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>3.2人月</t>
-        </is>
-      </c>
-      <c r="D41" s="20" t="inlineStr"/>
-      <c r="E41" s="21" t="n">
-        <v>2790000</v>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>5. インフラ構築・デプロイ</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
+      <c r="E42" s="7" t="n">
+        <v>90000</v>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Vercelデプロイ設定</t>
+          <t>Supabase 本番環境構築 + RLS 設計</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>インフラ 0.1人月</t>
+          <t>インフラ 0.15人月</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
         <v>900000</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>90000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Supabase本番環境構築</t>
+          <t>LiveKit Cloud Build → Ship 昇格 + Egress 設定</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -1649,12 +1657,12 @@
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>LiveKit Cloud設定・接続</t>
+          <t>環境変数管理・CI/CD・Vercel cron 設定</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
@@ -1672,12 +1680,12 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>環境変数管理・CI/CD</t>
+          <t>ドメイン・SSL・DNS 設定 (お名前.com)</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -1693,169 +1701,169 @@
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>5-5</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>ドメイン・SSL・DNS設定</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>インフラ 0.1人月</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="n">
+      <c r="A47" s="18" t="inlineStr"/>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>0.55人月</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr"/>
+      <c r="E47" s="21" t="n">
+        <v>495000</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>8. YouTube Live 連携・配信パイプライン (v2 新規)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>8-1</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>YouTube OAuth 検証申請 (3 scope) + デモ動画作成</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>BE 0.3人月</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
         <v>900000</v>
       </c>
-      <c r="E47" s="5" t="n">
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="18" t="inlineStr"/>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>小計</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>0.5人月</t>
-        </is>
-      </c>
-      <c r="D48" s="20" t="inlineStr"/>
-      <c r="E48" s="21" t="n">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>6. テスト</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
+      <c r="E49" s="5" t="n">
+        <v>270000</v>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>単体テスト・結合テスト</t>
+          <t>LiveKit Egress (RTMP push to YouTube Live)</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>QA 0.3人月</t>
+          <t>BE 0.4人月</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>550000</v>
+        <v>900000</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>165000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>ブラウザ互換性テスト（iOS/Android/PC）</t>
+          <t>YouTube Live broadcast 作成 / stream 連携 / 終了処理</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>QA 0.2人月</t>
+          <t>BE 0.3人月</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>550000</v>
+        <v>900000</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>110000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>ライブ配信E2Eテスト</t>
+          <t>視聴経路 YouTube iframe デフォルト切替 (PR #124)</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>QA 0.2人月</t>
+          <t>FE 0.15人月</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>550000</v>
+        <v>800000</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>110000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>セキュリティテスト</t>
+          <t>アーカイブ自動保存 + cron upload (旧パイプライン)</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>QA 0.15人月</t>
+          <t>BE 0.3人月</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>550000</v>
+        <v>900000</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>82500</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>パフォーマンステスト</t>
+          <t>Made for Kids ポリシー対応 + 配信ページ警告 UI</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>QA 0.15人月</t>
+          <t>FE+BE 0.15人月</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>550000</v>
+        <v>850000</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>82500</v>
+        <v>127500</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
@@ -1867,18 +1875,18 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>1.0人月</t>
+          <t>1.6人月</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr"/>
       <c r="E55" s="21" t="n">
-        <v>550000</v>
+        <v>1417500</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>7. プロジェクト管理</t>
+          <t>9. 配信品質改善 (v2 新規)</t>
         </is>
       </c>
       <c r="B56" s="13" t="n"/>
@@ -1889,138 +1897,691 @@
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>進捗管理・ミーティング</t>
+          <t>スコアボード Canvas 焼き込み + offscreen 最適化</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>PM 0.5人月</t>
+          <t>FE 0.6人月</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>500000</v>
+        <v>480000</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>仕様調整・変更管理</t>
+          <t>simulcast off + bitrate 調整 (PR #119/#123/#126)</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>PM 0.3人月</t>
+          <t>FE 0.2人月</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
+          <t>9-3</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>A/V drift 修正 (captureStream / framerate / rAF)</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>FE 0.5人月</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>9-4</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>iOS Safari 共有時 WebRTC バックグラウンド対策</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>FE 0.5人月</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>9-5</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>カメラレンズ切替 + zoom 物理レンズ対応 (PR #110)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>FE 0.3人月</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>体育館スポーツ音声処理 (RAW 配信 BAND 化)</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>FE 0.3人月</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="18" t="inlineStr"/>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>2.4人月</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr"/>
+      <c r="E63" s="21" t="n">
+        <v>1920000</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>10. 運用堅牢化・セキュリティ (v2 新規)</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>10-1</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>ストレイ broadcast 完全対策 (PR #125)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>BE 0.2人月</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>Supabase TOCTOU CAS guard (PR #76)</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>BE 0.15人月</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>RLS / 列レベル GRANT セキュリティ強化</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>BE 0.4人月</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>cron/cleanup 新パイプライン対応</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>BE 0.1人月</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>セキュリティ監査対応 (5/26 + 5/10)</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>BE 0.2人月</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="18" t="inlineStr"/>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>1.05人月</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr"/>
+      <c r="E70" s="21" t="n">
+        <v>945000</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>11. LP・SEO・共有 UI 最適化 (v2 新規)</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>11-1</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>LP ブラッシュアップ + リアルタイム訴求撤廃 (PR #122)</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>FE+デザイナー 0.4人月</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>750000</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>SEO 基盤 (Search Console / OG / JSON-LD / sitemap)</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>FE 0.3人月</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>11-3</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>共有 UI / LINE 共有 / QR コード生成</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>FE 0.2人月</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="18" t="inlineStr"/>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>0.9人月</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr"/>
+      <c r="E75" s="21" t="n">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>6. テスト</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>単体テスト・結合テスト</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>QA 0.4人月</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>ブラウザ互換性テスト（iOS/Android/PC/Safari/Chrome）</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>QA 0.3人月</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>6-3</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>ライブ配信 E2E テスト (実機含む)</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>QA 0.4人月</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>6-4</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>セキュリティテスト・脆弱性診断</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>QA 0.2人月</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>6-5</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>パフォーマンステスト・負荷試験</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>QA 0.2人月</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>550000</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="18" t="inlineStr"/>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>小計</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>1.5人月</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr"/>
+      <c r="E82" s="21" t="n">
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>7. プロジェクト管理</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>7-1</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>進捗管理・ミーティング・タスクトラッキング</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>PM 0.6人月</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>7-2</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>仕様調整・変更管理 (5/10 オーナーフィードバック対応含む)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>PM 0.4人月</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
           <t>7-3</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>納品・ドキュメント整備</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>納品・ドキュメント整備・運用引継ぎ</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>PM 0.2人月</t>
         </is>
       </c>
-      <c r="D59" s="5" t="n">
+      <c r="D86" s="7" t="n">
         <v>1000000</v>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E86" s="7" t="n">
         <v>200000</v>
       </c>
     </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="18" t="inlineStr"/>
-      <c r="B60" s="19" t="inlineStr">
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="18" t="inlineStr"/>
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
-        <is>
-          <t>1.0人月</t>
-        </is>
-      </c>
-      <c r="D60" s="20" t="inlineStr"/>
-      <c r="E60" s="21" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="22" t="inlineStr">
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>1.2人月</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr"/>
+      <c r="E87" s="21" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="22" t="inlineStr">
         <is>
           <t>開発費 合計（税抜）</t>
         </is>
       </c>
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n"/>
-      <c r="E62" s="24" t="n">
-        <v>7950000</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="25" t="inlineStr">
+      <c r="B89" s="23" t="n"/>
+      <c r="C89" s="23" t="n"/>
+      <c r="D89" s="23" t="n"/>
+      <c r="E89" s="24" t="n">
+        <v>13762500</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>消費税（10%）</t>
         </is>
       </c>
-      <c r="B63" s="26" t="n"/>
-      <c r="C63" s="26" t="n"/>
-      <c r="D63" s="26" t="n"/>
-      <c r="E63" s="27" t="n">
-        <v>795000</v>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="27" t="n">
+        <v>1376250</v>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>見積もり合計（税込）</t>
         </is>
       </c>
-      <c r="B64" s="28" t="n"/>
-      <c r="C64" s="28" t="n"/>
-      <c r="D64" s="28" t="n"/>
-      <c r="E64" s="9" t="n">
-        <v>8745000</v>
+      <c r="B91" s="28" t="n"/>
+      <c r="C91" s="28" t="n"/>
+      <c r="D91" s="28" t="n"/>
+      <c r="E91" s="9" t="n">
+        <v>15138750</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A89:D89"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A91:D91"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A90:D90"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A9:E9"/>
@@ -2037,19 +2598,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>残り開発費用見積もり（ローンチまでの8%分）</t>
+          <t>残り開発費用見積もり（5月中完璧化 → 6/1 正式ローンチ）</t>
         </is>
       </c>
     </row>
@@ -2091,16 +2652,16 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>YouTube録画・自動アップロード（Phase 2-3）</t>
+          <t>Google OAuth 認定通過対応 (✅ 2026-05-13 正式通過済・3 scope 承認)</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>0.5人月</t>
+          <t>BE 0.2人月</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>450000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="6">
@@ -2111,16 +2672,16 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>UI最終調整・バグ修正</t>
+          <t>配信プロトコル TCP 化 (B 案・MediaRecorder + 中継 server + RTMP)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>0.2人月</t>
+          <t>FE+BE 0.7人月</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>160000</v>
+        <v>595000</v>
       </c>
     </row>
     <row r="7">
@@ -2131,16 +2692,16 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>ベータテスト・品質保証</t>
+          <t>live_status='creating' 永遠固まり対処 (egress-webhook 改修)</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>0.3人月</t>
+          <t>BE 0.05人月</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>165000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="8">
@@ -2151,16 +2712,16 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>外部API利用料・インフラ増強</t>
+          <t>細部 UX 仕上げ (ストレイ警告 / 視聴 UI 調整)</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FE 0.2人月</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="9">
@@ -2171,61 +2732,101 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>ローンチ後保守運用・追加開発</t>
+          <t>実機検証 + バグ対応 (5月後半・実試合配信での確認)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
+          <t>QA 0.3人月</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>外部 API 利用料・追加インフラ (TCP 中継 server 等)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>290000</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="D10" s="7" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>ローンチ後 1ヶ月の保守運用・hotfix 対応</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>小計（税抜）</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="31" t="n">
-        <v>1365000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="n">
+        <v>1445000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>消費税（10%）</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="27" t="n">
-        <v>136500</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="27" t="n">
+        <v>144500</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>合計（税込）</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="9" t="n">
-        <v>1501500</v>
+      <c r="B15" s="28" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>1589500</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2238,7 +2839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2279,7 +2880,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>UIデザイナー</t>
+          <t>UI デザイナー</t>
         </is>
       </c>
       <c r="B5" s="33" t="inlineStr">
@@ -2327,7 +2928,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>QAテスター</t>
+          <t>QA テスター</t>
         </is>
       </c>
       <c r="B9" s="33" t="inlineStr">
@@ -2336,10 +2937,29 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>※ 中間値で算出。大手SIerの場合はこの1.5〜2倍になることもある。</t>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>WebRTC / 映像配信スペシャリスト</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>¥1,200,000〜1,500,000 (割増)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>※ 中間値で算出。大手 SIer の場合はこの 1.5〜2 倍になることもある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>※ WebRTC / 映像配信は LIVE SPOtCH のコア技術領域。対応エンジニアが限られるため割増単価が一般的。</t>
         </is>
       </c>
     </row>
